--- a/data/numeric/input/data_220/1_教育-全部.xlsx
+++ b/data/numeric/input/data_220/1_教育-全部.xlsx
@@ -45293,18 +45293,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A7596E-0B50-4456-B529-97BD9A10A4EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C14F547-53C8-4B09-8CD2-40E71C26714D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BAED13A-BAC8-4DE4-A34C-0731DD5A3A96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{717A4000-3534-4FD3-9FFB-7C2C14B76BFC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4D17D7-4DCE-4C09-A438-73F73F11330A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{486FD190-2302-48E5-B44C-DEF9C1E6C11C}"/>
 </file>